--- a/Result/profitability/1711.xlsx
+++ b/Result/profitability/1711.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.03</v>
       </c>
       <c r="M2" t="n">
-        <v>0.008750000000000001</v>
+        <v>0.0225</v>
       </c>
       <c r="N2" t="n">
-        <v>19.73125</v>
+        <v>20.0875</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>0.24</v>
       </c>
       <c r="M3" t="n">
-        <v>0.02875</v>
+        <v>0.0425</v>
       </c>
       <c r="N3" t="n">
-        <v>19.27375</v>
+        <v>19.6725</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -899,10 +899,10 @@
         <v>0.14</v>
       </c>
       <c r="M4" t="n">
-        <v>0.03625</v>
+        <v>0.05125</v>
       </c>
       <c r="N4" t="n">
-        <v>19.09875</v>
+        <v>19.42</v>
       </c>
       <c r="O4" t="n">
         <v>1</v>
@@ -1018,10 +1018,10 @@
         <v>-0.17</v>
       </c>
       <c r="M5" t="n">
-        <v>0.006249999999999995</v>
+        <v>0.04625</v>
       </c>
       <c r="N5" t="n">
-        <v>18.14125</v>
+        <v>18.7925</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>-0.13</v>
       </c>
       <c r="M6" t="n">
-        <v>0.006249999999999995</v>
+        <v>0.04375</v>
       </c>
       <c r="N6" t="n">
-        <v>17.11625</v>
+        <v>18.23375</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>0.24</v>
       </c>
       <c r="M7" t="n">
-        <v>0.05</v>
+        <v>0.07875</v>
       </c>
       <c r="N7" t="n">
-        <v>17.58625</v>
+        <v>18.49375</v>
       </c>
       <c r="O7" t="n">
         <v>1</v>
@@ -1391,10 +1391,10 @@
         <v>0.31</v>
       </c>
       <c r="M8" t="n">
-        <v>0.09375</v>
+        <v>0.10625</v>
       </c>
       <c r="N8" t="n">
-        <v>18.265</v>
+        <v>18.68625</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -1406,13 +1406,13 @@
         <v>1</v>
       </c>
       <c r="R8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S8" t="n">
         <v>1</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="U8" t="n">
         <v>0</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1711</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>2132</v>
+      </c>
+      <c r="D75" t="n">
+        <v>1601</v>
+      </c>
+      <c r="E75" t="n">
+        <v>531</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.89</v>
+      </c>
+      <c r="G75" t="n">
+        <v>111</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>5.19%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>10</v>
+      </c>
+      <c r="J75" t="n">
+        <v>121</v>
+      </c>
+      <c r="K75" t="n">
+        <v>104</v>
+      </c>
+      <c r="L75" t="n">
+        <v>0.19</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.02875</v>
+      </c>
+      <c r="N75" t="n">
+        <v>20.71625</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>1</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>1</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="X75" t="n">
+        <v>1.111111111111111</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>3.370000000000001</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>0.1565985130111525</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-2.461538461538462</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>5.210000000000001</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.2647357723577237</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
